--- a/forms/welpia/f16.xlsx
+++ b/forms/welpia/f16.xlsx
@@ -903,7 +903,11 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="n"/>
-      <c r="B11" s="2" t="n"/>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>退職理由（該当に○）：　一身上の都合　・　定年退職　・　契約期間満了　・　暫定支給決定期間満了</t>
+        </is>
+      </c>
       <c r="C11" s="2" t="n"/>
       <c r="D11" s="2" t="n"/>
       <c r="E11" s="2" t="n"/>
@@ -947,7 +951,7 @@
       <c r="F12" s="2" t="n"/>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>この度、一身上の都合により、　　　年　　　月　　　日をもちまして</t>
+          <t>上記の理由により、令和　　　年　　　月　　　日をもちまして</t>
         </is>
       </c>
       <c r="H12" s="2" t="n"/>
@@ -1021,7 +1025,11 @@
       <c r="AI13" s="2" t="n"/>
     </row>
     <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="7" t="n"/>
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>離職票：　　必要　　・　　必要無し　　（どちらかに○）</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="30" customHeight="1">
       <c r="A15" s="2" t="n"/>
